--- a/www/download/COUNTRY.ITA.zdW13.xlsx
+++ b/www/download/COUNTRY.ITA.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Itália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.840781231385862</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796666774552586</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.878518444762489</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.895479663178239</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.938262380506083</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08271976951272</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.11656987056528</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.05752963977825</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.884017009933639</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803923184260651</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803793929556715</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796432001820435</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.729660730035597</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902071681034</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948696375644</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21.841</t>
+          <t>-0.0351275985657629</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.966</t>
+          <t>-0.031874711805159</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.035</t>
+          <t>0.0463926618780335</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.253</t>
+          <t>0.0543895492547086</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.494</t>
+          <t>0.0634540537563089</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>0.0225073834510612</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>23.393</t>
+          <t>0.0263766154445118</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.793</t>
+          <t>0.0287765194323679</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>-0.000774592542623465</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.256</t>
+          <t>-0.100731587754584</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24.396</t>
+          <t>-0.0633609129035049</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>24.874</t>
+          <t>-0.0495287228222665</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25.188</t>
+          <t>0.0449512839811184</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>25.278</t>
+          <t>0.0702505429823594</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>25.079</t>
+          <t>0.162605432360634</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15.959</t>
+          <t>0.728787079878464</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.051</t>
+          <t>0.76760110323946</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.135</t>
+          <t>0.927782933057681</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.306</t>
+          <t>0.917865474668624</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.559</t>
+          <t>0.920043686129911</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.883</t>
+          <t>0.955337543270001</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17.315</t>
+          <t>0.785725466258767</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.717</t>
+          <t>0.715954942960415</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17.972</t>
+          <t>0.688062492227756</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18.029</t>
+          <t>0.450007280790621</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>18.359</t>
+          <t>0.43334950111676</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>18.796</t>
+          <t>0.40276052831184</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.469604044113352</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>0.508159677367337</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>0.666329073816806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40599.839</t>
+          <t>0.981584973199817</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41143.486</t>
+          <t>1.10843491811799</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41054.172</t>
+          <t>1.35831728448125</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41827.744</t>
+          <t>1.4088686626705</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>42189.165</t>
+          <t>1.40774794919092</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42680.822</t>
+          <t>1.4325977530046</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>43115.103</t>
+          <t>1.31137440094764</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43564.346</t>
+          <t>1.25840959022602</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>44087.232</t>
+          <t>0.802404438399684</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>44292.887</t>
+          <t>0.927894357412414</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>44369.551</t>
+          <t>0.929552782523593</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>45142.592</t>
+          <t>0.912681470988137</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>45750.837</t>
+          <t>0.977481614057802</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>45573.368</t>
+          <t>0.890149743109295</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>44374.474</t>
+          <t>1.08503945645491</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26426.569</t>
+          <t>49874969554.6232</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26837.401</t>
+          <t>49344427430.4855</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>46931762112.5945</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>27355.531</t>
+          <t>48313435322.7035</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>27748.134</t>
+          <t>48605835596.4291</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28310.735</t>
+          <t>51525097107.3097</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28707.965</t>
+          <t>51293798822.0109</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>29182.183</t>
+          <t>50632319813.612</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29479.918</t>
+          <t>52513434934.3098</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29718.084</t>
+          <t>54727990678.2597</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>30039.004</t>
+          <t>54309239002.2856</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30792.788</t>
+          <t>58514261363.5063</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>31249.713</t>
+          <t>58844262779.5437</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>31549.881</t>
+          <t>59506576141.6352</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>30509.279</t>
+          <t>48538508718.8212</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>15364839348.6752</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>15143358672.6266</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>13897434823.7065</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>14174070753.8437</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>14506002829.9653</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>14845857317.4417</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>15889489850.9463</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>16620779767.0552</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>18602639876.0336</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>20016257678.6402</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>20365111034.7442</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>21173894333.7873</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>15.72</t>
+          <t>20480656510.2852</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20792173855.7271</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>18307840090.8573</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>928272.387123979</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>853532.491437212</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>850848.244836127</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>860259.345923799</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>901427.10686922</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>1005763.79652802</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>998567.542853172</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>929121.336533884</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>796582.634737724</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>725618.163318066</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>690499.041051795</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>697557.026853225</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>605655.565839726</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>551522.066538358</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>546844.835696312</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>55.46</t>
+          <t>175773.02924986</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>176565.261684106</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>176203.302166586</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>177108.170767099</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>183525.285307883</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>184663.045186097</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>180947.782733426</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>184668.094892894</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>197528.057251104</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>218810.454788617</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>234118.57920054</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>247954.622189121</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>283013.429138381</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>307390.037598834</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>271534.29954086</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>429746.108216222</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>428218.011037852</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>405973.900402304</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>413709.868128396</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>432931.034005299</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>466521.904464321</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>451042.879934504</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>454945.077479949</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>505837.130075479</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>579840.085209978</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>616290.781685597</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>693200.064048817</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>785460.873922504</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>869613.810244264</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>661238.07688035</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.719937846423274</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>0.772222502298106</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>0.93265878492795</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>0.929969962410539</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>0.912872520793958</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>42.89</t>
+          <t>0.906978761458192</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>0.806726689736384</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>0.755764988706686</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>0.584716910957349</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>0.484697308414089</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>0.475022868706755</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>0.454280814600257</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.525815995415318</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>0.517392131237387</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.666459792558273</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>52.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>49.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>48.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.840781231385862</t>
+          <t>962.799721068722</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.796666774552586</t>
+          <t>943.4350284791</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.878518444762489</t>
+          <t>861.322269829967</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.895479663178239</t>
+          <t>869.23892936127</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262380506083</t>
+          <t>876.01925417992</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976951272</t>
+          <t>879.342844975786</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987056528</t>
+          <t>917.68255197555</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963977825</t>
+          <t>938.115490430497</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017009933639</t>
+          <t>1035.11317167273</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923184260651</t>
+          <t>1110.21330278882</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793929556715</t>
+          <t>1109.24709057726</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432001820435</t>
+          <t>1126.49867174149</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660730035597</t>
+          <t>1071.15844113185</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902071681034</t>
+          <t>1077.8676033679</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948696375644</t>
+          <t>961.884701594429</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>21914867406.0924</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>23296517528.8653</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>19021942216.758</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>20397487146.5768</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>19427909199.0406</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>19971390003.9164</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>22048577155.302</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>22544616734.288</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>25721332581.3041</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>28958114278.7871</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>27383815466.5097</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>27987896102.6475</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>28326694449.2415</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>27946949261.0942</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>22466267817.9221</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>21667673812.6654</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>22855940434.9967</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>18599963359.3343</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>20632567517.7596</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>19799531350.8348</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>20265826837.6562</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>22203967204.3498</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>22874479316.9792</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>26013405935.3765</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>28838849786.1144</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>27543848610.1073</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>28266360062.7193</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>29020807316.5367</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>28674241557.1088</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>22864186946.782</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.926</t>
+          <t>247193593.426975</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.313</t>
+          <t>440577093.868592</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4.051</t>
+          <t>421978857.423712</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>-235080371.182814</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.956</t>
+          <t>-371622151.794185</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.539</t>
+          <t>-294436833.739765</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>-155390049.047829</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.901</t>
+          <t>-329862582.691227</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.834</t>
+          <t>-292073354.072466</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>119264492.672733</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.693</t>
+          <t>-160033143.597627</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.919</t>
+          <t>-278463960.071814</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.729</t>
+          <t>-694112867.295183</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-727292296.014632</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-397919128.859858</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>1655.95567879187</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>1671.97678692692</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.224</t>
+          <t>1664.64205144097</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.279</t>
+          <t>1677.60502382515</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>1675.71315900719</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.138</t>
+          <t>1676.88812940905</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>1658.00155935962</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>1647.11033346127</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.927</t>
+          <t>1640.36134790447</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>1648.33070241608</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.474</t>
+          <t>1636.1648256479</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.683</t>
+          <t>1638.24540598632</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>1634.39068310312</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.619</t>
+          <t>1635.54781986615</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.021</t>
+          <t>1602.94218028403</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>1858.86486090508</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1873.05315487572</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1863.16002486986</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1879.67894538166</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1875.58249125318</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>1861.34478262197</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1843.06879490314</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>1830.96554463269</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1825.58848593766</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1826.05148807929</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1818.73728264701</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1814.84324256958</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1816.38154431294</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>1802.90548506606</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.908</t>
+          <t>1769.40115284424</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>264094.051320262</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>284159.037820871</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>273709.314934043</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>279199.718799629</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>267446.112383629</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>271816.639549609</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>278622.926817104</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>289676.973552407</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>341425.323118483</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-10.07</t>
+          <t>405297.403200335</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>428302.320226843</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>481657.008501385</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>574777.868225327</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>620446.232596912</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>467638.55616313</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>8998469702.55007</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>8785185463.26983</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>92.78</t>
+          <t>8401838821.10238</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>91.79</t>
+          <t>8734014368.15713</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>8514886617.8162</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>95.53</t>
+          <t>9769785029.45615</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>9909143356.62132</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>9570625364.99135</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>9761154453.97552</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10520930646.0691</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>10668309895.2901</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>40.28</t>
+          <t>12056534523.9421</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>12667296232.8211</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>12653837060.7588</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>9087165141.79814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>98.16</t>
+          <t>228255.448858</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>110.84</t>
+          <t>232407.002732804</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>135.83</t>
+          <t>232698.198545268</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>140.89</t>
+          <t>245836.958654195</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>140.77</t>
+          <t>248998.501493306</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>143.26</t>
+          <t>265066.114677891</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>131.14</t>
+          <t>266618.694809451</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>125.84</t>
+          <t>280372.844760904</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>334460.20865113</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>92.79</t>
+          <t>395652.878511208</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>429718.544386225</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>496999.274809229</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>97.75</t>
+          <t>577897.951572278</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>89.01</t>
+          <t>633477.962188218</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>476147.312084785</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>40599.839</t>
+          <t>25974088657.8169</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>41143.486</t>
+          <t>25240682613.8764</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>41054.172</t>
+          <t>22461113847.6778</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41827.744</t>
+          <t>24849245881.4912</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>42189.165</t>
+          <t>25519269941.4608</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>42680.822</t>
+          <t>28843228250.5601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>43115.103</t>
+          <t>30275334817.2854</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>43564.346</t>
+          <t>30825740043.1868</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>44087.232</t>
+          <t>34565361913.8066</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>44292.887</t>
+          <t>38311126607.6243</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>44369.551</t>
+          <t>38210957662.3037</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>45142.592</t>
+          <t>41618203746.2928</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>45750.837</t>
+          <t>41277253423.2804</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>45573.368</t>
+          <t>41665911503.9025</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>44374.474</t>
+          <t>32319320826.1146</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>26426.569</t>
+          <t>35838.6024622619</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26837.401</t>
+          <t>51752.035088067</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>41011.1163887754</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>27355.531</t>
+          <t>33362.7601454339</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>27748.134</t>
+          <t>18447.6108903229</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28310.735</t>
+          <t>6750.52487171849</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>28707.965</t>
+          <t>12004.232007653</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>29182.183</t>
+          <t>9304.12879150281</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29479.918</t>
+          <t>6965.1144673525</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29718.084</t>
+          <t>9644.52468912682</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>30039.004</t>
+          <t>-1416.22415938166</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>30792.788</t>
+          <t>-15342.2663078439</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>31249.713</t>
+          <t>-3120.08334695161</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>31549.881</t>
+          <t>-13031.7295913069</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>30509.279</t>
+          <t>-8508.7559216558</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49874.97</t>
+          <t>-16975618955.2668</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49344.427</t>
+          <t>-16455497150.6066</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>46931.762</t>
+          <t>-14059275026.5754</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48313.435</t>
+          <t>-16115231513.3341</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>48605.836</t>
+          <t>-17004383323.6446</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>51525.097</t>
+          <t>-19073443221.1039</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51293.799</t>
+          <t>-20366191460.6641</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>50632.32</t>
+          <t>-21255114678.1954</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>52513.435</t>
+          <t>-24804207459.8311</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>54727.991</t>
+          <t>-27790195961.5553</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>54309.239</t>
+          <t>-27542647767.0136</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>58514.261</t>
+          <t>-29561669222.3507</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>58844.263</t>
+          <t>-28609957190.4592</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>59506.576</t>
+          <t>-29012074443.1438</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>48538.509</t>
+          <t>-23232155684.3165</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>481645.38184</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>537495.33571</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>505213.28784</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>511530.97657</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>492188.79518</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>445777.23828</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>451330.4098</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>491428.51881</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>598035.25537</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>681849.93883</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>695307.47941</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>728001.0722</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>831977.77466</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>900160.78119</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>799653.89402</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20399.66</t>
+          <t>0.0854440640998736</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20345.972</t>
+          <t>0.0880880932438392</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20369.614</t>
+          <t>0.0875949526497047</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20682.862</t>
+          <t>0.0944243957200937</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20604.667</t>
+          <t>0.0954757072824388</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20395.144</t>
+          <t>0.100927520029338</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20577.864</t>
+          <t>0.104614688059056</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20552.314</t>
+          <t>0.103031207999922</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20506.357</t>
+          <t>0.101163427386847</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>20652.343</t>
+          <t>0.103167613281961</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20631.173</t>
+          <t>0.0998849215341868</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>20930.295</t>
+          <t>0.0989594602125103</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>21202.478</t>
+          <t>0.100143441873825</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>21034.313</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>19932.11</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>465340.671482329</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>521488.798651422</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>496303.293015968</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>483449.282630376</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>477855.563537439</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>431683.994937708</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>441795.012050519</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>487938.915002717</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>606583.421349111</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>690968.940876866</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>724059.701269968</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>764489.446355203</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>867055.557783028</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>967793.77757274</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>912973.106233138</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15364.839</t>
+          <t>679733.554643271</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15143.359</t>
+          <t>758441.257490796</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13897.435</t>
+          <t>717904.276715278</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14174.071</t>
+          <t>703585.461813047</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14506.003</t>
+          <t>693857.950583344</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14845.857</t>
+          <t>625554.88267815</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15889.49</t>
+          <t>636125.742097246</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16620.78</t>
+          <t>700131.441621817</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18602.64</t>
+          <t>872621.151126705</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20016.258</t>
+          <t>988910.628243449</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20365.111</t>
+          <t>1029297.71456805</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>21173.894</t>
+          <t>1077681.83988703</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>20480.657</t>
+          <t>1221323.84656418</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>20792.174</t>
+          <t>1365623.42467672</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>18307.84</t>
+          <t>1295764.70313376</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>3926439.23683898</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>4312841.93526092</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>93.27</t>
+          <t>4051046.55166359</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>4085394.52495392</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>3956020.15316128</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>3539065.09857788</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80.67</t>
+          <t>3533085.32234121</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>3900647.95463223</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>4834248.85836636</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>5510229.03828239</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>5693345.01691844</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>5918710.30586855</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>52.58</t>
+          <t>6729429.19981627</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>51.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>66.65</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>679733.554643271</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>684865.116035224</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>701696.991021963</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>684893.370012139</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>695002.998970758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>709862.782248644</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>716801.079457236</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>724230.600223024</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>727772.272550221</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>736509.319033262</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>755398.524855962</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>775456.249202919</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>784326.25792096</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>793857.456750158</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>771062.532633701</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>465340.671482329</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>470500.676099497</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>483677.566638523</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>467597.759430376</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>475807.863984618</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>486782.646277826</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>494757.91598442</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>502468.140800356</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>504035.435613977</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>512125.580951395</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>528054.878442189</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>546208.501622052</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>552725.117295964</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>558479.781745749</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>539168.337124448</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>335490.925836729</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>379910.022539204</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>354851.230874722</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>385760.909296953</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>377703.822146656</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>357189.06362185</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>369612.618882754</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>401888.470748183</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>489049.183353295</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>568477.178516551</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>568679.320281951</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>585712.377022974</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>673908.201915822</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>706935.604343281</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>611939.406586245</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>26426568700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>26837401000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>26858999500</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>27355530800</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>27748134200</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>28310734600</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>28707965400</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>29182183200</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>29479918000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>29718083900</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>30039004500</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>30792788300</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>31249713300</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>31549881000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>30509279400</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>40599839200</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>41143485600</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>41054172200</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>41827743700</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>42189165000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>42680822000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>43115102911.5583</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>43564346300</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>44087231700</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>44292887500</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>44369551000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>45142592300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>45750836700</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>45573368085.9512</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>44374474453.1903</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20399659973.0691</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20345972185.5228</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20369613545.4545</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>20682862103.7944</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20604667128.9301</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>20395143817.0313</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20577864273.4922</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20552313900.7907</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>20506357017.7394</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>20652343353.669</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20631173222.9741</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20930294616.9981</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>21202477611.8916</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>21034312544.3434</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>19932109820.2697</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>21841200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21966000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22034700</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>22252600</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22493900</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>22930100</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>23393105.5806433</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>23793100</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>24149600</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>24256100</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>24395800</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>24874100</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>25187900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>25277735.5571035</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>25078809.506742</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15958500</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>16051300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16135000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>16306300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>16559000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>16882900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>17314800</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>17717200</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>17971600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>18029200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18359400</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>18796200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>19120100</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>19290100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>19033300</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>40599839200</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>41143485600</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>41054172200</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>41827743700</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>42189165000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>42680822000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>43115102911.5583</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>43564346300</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>44087231700</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>44292887500</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>44369551000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>45142592300</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>45750836700</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>45573368085.9512</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>44374474453.1903</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>26426568700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>26837401000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>26858999500</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>27355530800</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>27748134200</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>28310734600</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>28707965400</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>29182183200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>29479918000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>29718083900</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>30039004500</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>30792788300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>31249713300</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>31549881000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>30509279400</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.115064863872481</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.122824041380863</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.131178552927775</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.139855419341338</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.151165718831045</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.158276403090031</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.148063865432393</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.148378488449053</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.138874929593949</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.141980402819401</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.150523193471181</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.155456241362467</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.157207962015697</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.176976462989848</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.171778646838757</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.330346728312496</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.34945440899313</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.369075878158331</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.389581381411308</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.396906296214269</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.418701443239057</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.411514557796667</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.422333833744622</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.39435686951909</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.463301239446308</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.468235395421219</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.476813202042057</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.479029026662959</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.462192916504095</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.473675289854856</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.554588407815023</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.527721549626007</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.499745568913894</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.470563199247354</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.451927984954686</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.423022153670912</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.44042157677094</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.429287677806325</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.466768200886961</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.39471835773429</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.3812414111076</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.367730556595476</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.363763011321344</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.360830620506057</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.354546063306387</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0717110126405763</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0753669150529157</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0793565771445653</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0832941413248145</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0899404408524558</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0910168375199489</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0937301852919814</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0974894162572822</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.102150559963198</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0971776740057303</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.108058588631121</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.115701311228379</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.121575422221856</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.135136273934228</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.131157776772808</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.356683496787542</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.369457860635674</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.382425513470241</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.394586737653297</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.404867465876106</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.428904162541322</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.408024071566911</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.412802153543048</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.426547959811869</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.451321405838827</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.454828719520867</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.462073554632459</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.463345443318637</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.462893831730371</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.474074665641196</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.571605490571882</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.55517522431141</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.538217909385193</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.522119121021889</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.505192093271439</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.480078999938729</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.498245743141107</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.48970843019967</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.471301480224933</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.451500920155443</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.437112691848013</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.422225134139162</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.415079134459507</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.401969894335401</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.394767557585996</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2104988.71341</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2324819.29448</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2224223.78423</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2278989.53668</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2273650.16017</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2137660.35747</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2182848.1148</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2378133.78076</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2927417.2305</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3357865.69895</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3474255.19799</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3682927.63676</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4212757.68836</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4618580.06788</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4020984.88656</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1015224.48048</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1138351.28003</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1072755.50759</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1089346.37111</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1071561.77273</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>982743.9463</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1005738.36098</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1102019.91237</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1361670.33448</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1557387.80676</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1597977.03485</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1663394.21691</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1895232.04848</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2072559.02902</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1907704.10972</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3301276.40726932</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3359351.1456276</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3418930.21646495</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3485263.46500361</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3558016.62368352</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3643776.52409036</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3730129.56765716</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3817527.93087565</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3893438.56161742</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3975552.41871637</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4059826.08095388</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4150495.72163218</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4239740.68000487</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
